--- a/projects/NZIPL/docs/trade_data/latest_2024/NZIPL_2024_RoleStage_Balance_USDmn.xlsx
+++ b/projects/NZIPL/docs/trade_data/latest_2024/NZIPL_2024_RoleStage_Balance_USDmn.xlsx
@@ -94,7 +94,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-10</t>
+    <t xml:space="preserve">2026-07-11</t>
   </si>
   <si>
     <t xml:space="preserve">ISO3</t>
@@ -7692,7 +7692,7 @@
         <v>38</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1171.682</v>
+        <v>2343.363</v>
       </c>
     </row>
     <row r="9">
@@ -7811,7 +7811,7 @@
         <v>38</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-143.473</v>
+        <v>-286.946</v>
       </c>
     </row>
     <row r="16">
@@ -7930,7 +7930,7 @@
         <v>38</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>818.526</v>
+        <v>1637.052</v>
       </c>
     </row>
     <row r="23">
@@ -8049,7 +8049,7 @@
         <v>38</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>-188.578</v>
+        <v>-377.155</v>
       </c>
     </row>
     <row r="30">
@@ -8168,7 +8168,7 @@
         <v>38</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>-61.125</v>
+        <v>-122.251</v>
       </c>
     </row>
     <row r="37">
@@ -8287,7 +8287,7 @@
         <v>38</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>-40.269</v>
+        <v>-80.537</v>
       </c>
     </row>
     <row r="44">
@@ -8406,7 +8406,7 @@
         <v>38</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>-35.808</v>
+        <v>-71.616</v>
       </c>
     </row>
     <row r="51">
@@ -8525,7 +8525,7 @@
         <v>38</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>-61.295</v>
+        <v>-122.59</v>
       </c>
     </row>
     <row r="58">
@@ -8644,7 +8644,7 @@
         <v>38</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>10.496</v>
+        <v>20.992</v>
       </c>
     </row>
     <row r="65">
@@ -8763,7 +8763,7 @@
         <v>38</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>-299.14</v>
+        <v>-598.28</v>
       </c>
     </row>
     <row r="72">
@@ -8882,7 +8882,7 @@
         <v>38</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>1.82</v>
+        <v>3.641</v>
       </c>
     </row>
     <row r="79">
@@ -9001,7 +9001,7 @@
         <v>38</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>133.015</v>
+        <v>266.03</v>
       </c>
     </row>
     <row r="86">
@@ -9120,7 +9120,7 @@
         <v>38</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>-14.271</v>
+        <v>-28.542</v>
       </c>
     </row>
     <row r="93">
@@ -9239,7 +9239,7 @@
         <v>38</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>-65.941</v>
+        <v>-131.883</v>
       </c>
     </row>
     <row r="100">
@@ -9358,7 +9358,7 @@
         <v>38</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>196.716</v>
+        <v>393.432</v>
       </c>
     </row>
     <row r="107">
@@ -9477,7 +9477,7 @@
         <v>38</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>-177.075</v>
+        <v>-354.149</v>
       </c>
     </row>
     <row r="114">
@@ -9596,7 +9596,7 @@
         <v>38</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>-171.003</v>
+        <v>-342.006</v>
       </c>
     </row>
     <row r="121">
@@ -9715,7 +9715,7 @@
         <v>38</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>-0.101</v>
+        <v>-0.201</v>
       </c>
     </row>
     <row r="128">
@@ -9834,7 +9834,7 @@
         <v>38</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>-41.96</v>
+        <v>-83.921</v>
       </c>
     </row>
     <row r="135">
@@ -9953,7 +9953,7 @@
         <v>38</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>-193.263</v>
+        <v>-386.525</v>
       </c>
     </row>
     <row r="142">
@@ -10072,7 +10072,7 @@
         <v>38</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>-0.722</v>
+        <v>-1.444</v>
       </c>
     </row>
     <row r="149">
@@ -10191,15 +10191,15 @@
         <v>38</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>-7.662</v>
+        <v>-15.324</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B156" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C156" t="s">
         <v>31</v>
@@ -10208,15 +10208,15 @@
         <v>32</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>-223.2</v>
+        <v>-796.286</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B157" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C157" t="s">
         <v>33</v>
@@ -10225,15 +10225,15 @@
         <v>34</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>-5.191</v>
+        <v>7.435</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B158" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C158" t="s">
         <v>33</v>
@@ -10242,15 +10242,15 @@
         <v>35</v>
       </c>
       <c r="E158" s="2" t="n">
-        <v>28.909</v>
+        <v>539.435</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B159" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C159" t="s">
         <v>33</v>
@@ -10259,15 +10259,15 @@
         <v>36</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>-3180.111</v>
+        <v>563.986</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B160" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C160" t="s">
         <v>37</v>
@@ -10276,15 +10276,15 @@
         <v>34</v>
       </c>
       <c r="E160" s="2" t="n">
-        <v>-183.578</v>
+        <v>73.962</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B161" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C161" t="s">
         <v>37</v>
@@ -10293,15 +10293,15 @@
         <v>36</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>-337.321</v>
+        <v>-694.636</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B162" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C162" t="s">
         <v>38</v>
@@ -10310,15 +10310,15 @@
         <v>38</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>0.623</v>
+        <v>-131.706</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B163" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C163" t="s">
         <v>31</v>
@@ -10327,15 +10327,15 @@
         <v>32</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>-796.286</v>
+        <v>-223.2</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B164" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C164" t="s">
         <v>33</v>
@@ -10344,15 +10344,15 @@
         <v>34</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>7.435</v>
+        <v>-5.191</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B165" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C165" t="s">
         <v>33</v>
@@ -10361,15 +10361,15 @@
         <v>35</v>
       </c>
       <c r="E165" s="2" t="n">
-        <v>539.435</v>
+        <v>28.909</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B166" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C166" t="s">
         <v>33</v>
@@ -10378,15 +10378,15 @@
         <v>36</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>563.986</v>
+        <v>-3180.111</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B167" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C167" t="s">
         <v>37</v>
@@ -10395,15 +10395,15 @@
         <v>34</v>
       </c>
       <c r="E167" s="2" t="n">
-        <v>73.962</v>
+        <v>-183.578</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B168" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C168" t="s">
         <v>37</v>
@@ -10412,15 +10412,15 @@
         <v>36</v>
       </c>
       <c r="E168" s="2" t="n">
-        <v>-694.636</v>
+        <v>-337.321</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B169" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C169" t="s">
         <v>38</v>
@@ -10429,7 +10429,7 @@
         <v>38</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>-65.853</v>
+        <v>1.245</v>
       </c>
     </row>
     <row r="170">
@@ -10548,7 +10548,7 @@
         <v>38</v>
       </c>
       <c r="E176" s="2" t="n">
-        <v>-257.739</v>
+        <v>-515.477</v>
       </c>
     </row>
     <row r="177">
@@ -10667,7 +10667,7 @@
         <v>38</v>
       </c>
       <c r="E183" s="2" t="n">
-        <v>-0.058</v>
+        <v>-0.115</v>
       </c>
     </row>
     <row r="184">
@@ -10888,7 +10888,7 @@
         <v>38</v>
       </c>
       <c r="E196" s="2" t="n">
-        <v>-0.057</v>
+        <v>-0.114</v>
       </c>
     </row>
     <row r="197">
@@ -11007,7 +11007,7 @@
         <v>38</v>
       </c>
       <c r="E203" s="2" t="n">
-        <v>-0.074</v>
+        <v>-0.148</v>
       </c>
     </row>
     <row r="204">
@@ -11126,7 +11126,7 @@
         <v>38</v>
       </c>
       <c r="E210" s="2" t="n">
-        <v>-0.203</v>
+        <v>-0.406</v>
       </c>
     </row>
   </sheetData>
@@ -11280,7 +11280,7 @@
         <v>38</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>33386.9</v>
+        <v>33761.367</v>
       </c>
     </row>
     <row r="9">
@@ -11399,7 +11399,7 @@
         <v>38</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-1672.286</v>
+        <v>-1677.15</v>
       </c>
     </row>
     <row r="16">
@@ -11518,7 +11518,7 @@
         <v>38</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-9057.379</v>
+        <v>-9063.585</v>
       </c>
     </row>
     <row r="23">
@@ -11637,7 +11637,7 @@
         <v>38</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>-9342.69</v>
+        <v>-9346.733</v>
       </c>
     </row>
     <row r="30">
@@ -11756,7 +11756,7 @@
         <v>38</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>546.909</v>
+        <v>599.16</v>
       </c>
     </row>
     <row r="37">
@@ -11875,7 +11875,7 @@
         <v>38</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>102.864</v>
+        <v>101.018</v>
       </c>
     </row>
     <row r="44">
@@ -11994,7 +11994,7 @@
         <v>38</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>-336.647</v>
+        <v>-341.776</v>
       </c>
     </row>
     <row r="51">
@@ -12113,7 +12113,7 @@
         <v>38</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>-619.521</v>
+        <v>-637.822</v>
       </c>
     </row>
     <row r="58">
@@ -12232,7 +12232,7 @@
         <v>38</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>-855.815</v>
+        <v>-860.585</v>
       </c>
     </row>
     <row r="65">
@@ -12351,7 +12351,7 @@
         <v>38</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>-1544.595</v>
+        <v>-1536.297</v>
       </c>
     </row>
     <row r="72">
@@ -12470,7 +12470,7 @@
         <v>38</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>-1248.256</v>
+        <v>-1247.525</v>
       </c>
     </row>
     <row r="79">
@@ -12589,7 +12589,7 @@
         <v>38</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>-858.313</v>
+        <v>-855.791</v>
       </c>
     </row>
     <row r="86">
@@ -12708,7 +12708,7 @@
         <v>38</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>-283.532</v>
+        <v>-527.679</v>
       </c>
     </row>
     <row r="93">
@@ -12827,7 +12827,7 @@
         <v>38</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>-1351.46</v>
+        <v>-1351.264</v>
       </c>
     </row>
     <row r="100">
@@ -12946,7 +12946,7 @@
         <v>38</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>-277.705</v>
+        <v>-283.909</v>
       </c>
     </row>
     <row r="107">
@@ -13065,7 +13065,7 @@
         <v>38</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>-705.225</v>
+        <v>-704.198</v>
       </c>
     </row>
     <row r="114">
@@ -13184,7 +13184,7 @@
         <v>38</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>-2561.042</v>
+        <v>-2568.485</v>
       </c>
     </row>
     <row r="121">
@@ -13303,7 +13303,7 @@
         <v>38</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>63.822</v>
+        <v>71.531</v>
       </c>
     </row>
     <row r="128">
@@ -13422,7 +13422,7 @@
         <v>38</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>-842.109</v>
+        <v>-848.428</v>
       </c>
     </row>
     <row r="135">
@@ -13541,7 +13541,7 @@
         <v>38</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>-176.677</v>
+        <v>-174.589</v>
       </c>
     </row>
     <row r="142">
@@ -13660,7 +13660,7 @@
         <v>38</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>-191.621</v>
+        <v>-192.929</v>
       </c>
     </row>
     <row r="149">
@@ -13779,7 +13779,7 @@
         <v>38</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>520.536</v>
+        <v>508.223</v>
       </c>
     </row>
     <row r="156">
@@ -13898,7 +13898,7 @@
         <v>38</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>-27.255</v>
+        <v>-28.993</v>
       </c>
     </row>
     <row r="163">
@@ -14017,7 +14017,7 @@
         <v>38</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>2854.112</v>
+        <v>2855.036</v>
       </c>
     </row>
     <row r="170">
@@ -14136,7 +14136,7 @@
         <v>38</v>
       </c>
       <c r="E176" s="2" t="n">
-        <v>157.576</v>
+        <v>154.807</v>
       </c>
     </row>
     <row r="177">
@@ -14255,7 +14255,7 @@
         <v>38</v>
       </c>
       <c r="E183" s="2" t="n">
-        <v>-127.052</v>
+        <v>-115.4</v>
       </c>
     </row>
     <row r="184">
@@ -14374,7 +14374,7 @@
         <v>38</v>
       </c>
       <c r="E190" s="2" t="n">
-        <v>-740.059</v>
+        <v>-741.742</v>
       </c>
     </row>
     <row r="191">
@@ -14493,7 +14493,7 @@
         <v>38</v>
       </c>
       <c r="E197" s="2" t="n">
-        <v>-783.673</v>
+        <v>-787.499</v>
       </c>
     </row>
     <row r="198">
@@ -14612,7 +14612,7 @@
         <v>38</v>
       </c>
       <c r="E204" s="2" t="n">
-        <v>-415.233</v>
+        <v>-414.598</v>
       </c>
     </row>
     <row r="205">
@@ -14731,7 +14731,7 @@
         <v>38</v>
       </c>
       <c r="E211" s="2" t="n">
-        <v>-570.879</v>
+        <v>-568.84</v>
       </c>
     </row>
   </sheetData>
@@ -14851,7 +14851,7 @@
         <v>38</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2303.497</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="7">
@@ -14936,7 +14936,7 @@
         <v>38</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>709.476</v>
+        <v>1521.077</v>
       </c>
     </row>
     <row r="12">
@@ -15021,7 +15021,7 @@
         <v>38</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>672.202</v>
+        <v>1335.27</v>
       </c>
     </row>
     <row r="17">
@@ -15106,7 +15106,7 @@
         <v>38</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>6.423</v>
+        <v>11.518</v>
       </c>
     </row>
     <row r="22">
@@ -15191,7 +15191,7 @@
         <v>38</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-409.507</v>
+        <v>-664.267</v>
       </c>
     </row>
     <row r="27">
@@ -15276,7 +15276,7 @@
         <v>38</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>-691.931</v>
+        <v>-1350.389</v>
       </c>
     </row>
     <row r="32">
@@ -15361,7 +15361,7 @@
         <v>38</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>-202.602</v>
+        <v>-376.01</v>
       </c>
     </row>
     <row r="37">
@@ -15446,7 +15446,7 @@
         <v>38</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>-53.136</v>
+        <v>33.749</v>
       </c>
     </row>
     <row r="42">
@@ -15531,15 +15531,15 @@
         <v>38</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>-934.913</v>
+        <v>-1929.827</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B47" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C47" t="s">
         <v>31</v>
@@ -15548,15 +15548,15 @@
         <v>32</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>1569.108</v>
+        <v>-227.682</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B48" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C48" t="s">
         <v>33</v>
@@ -15565,15 +15565,15 @@
         <v>34</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>-10.032</v>
+        <v>-51.026</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B49" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C49" t="s">
         <v>33</v>
@@ -15582,15 +15582,15 @@
         <v>35</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>8266.999</v>
+        <v>-49.575</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B50" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C50" t="s">
         <v>37</v>
@@ -15599,15 +15599,15 @@
         <v>34</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>-110.846</v>
+        <v>-249.357</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B51" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C51" t="s">
         <v>38</v>
@@ -15616,15 +15616,15 @@
         <v>38</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>61.425</v>
+        <v>962.568</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B52" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C52" t="s">
         <v>31</v>
@@ -15633,15 +15633,15 @@
         <v>32</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>-227.682</v>
+        <v>1569.108</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B53" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C53" t="s">
         <v>33</v>
@@ -15650,15 +15650,15 @@
         <v>34</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>-51.026</v>
+        <v>-10.032</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B54" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C54" t="s">
         <v>33</v>
@@ -15667,15 +15667,15 @@
         <v>35</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>-49.575</v>
+        <v>8266.999</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B55" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C55" t="s">
         <v>37</v>
@@ -15684,15 +15684,15 @@
         <v>34</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>-249.357</v>
+        <v>-110.846</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B56" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C56" t="s">
         <v>38</v>
@@ -15701,7 +15701,7 @@
         <v>38</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>462.088</v>
+        <v>61.481</v>
       </c>
     </row>
     <row r="57">
@@ -15786,7 +15786,7 @@
         <v>38</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>-1424.668</v>
+        <v>-1536.926</v>
       </c>
     </row>
     <row r="62">
@@ -16041,7 +16041,7 @@
         <v>38</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>514.761</v>
+        <v>1028.065</v>
       </c>
     </row>
     <row r="77">
@@ -16126,7 +16126,7 @@
         <v>38</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>-96.175</v>
+        <v>-190.551</v>
       </c>
     </row>
     <row r="82">
@@ -16211,7 +16211,7 @@
         <v>38</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>-31.448</v>
+        <v>-31.57</v>
       </c>
     </row>
     <row r="87">
@@ -16296,7 +16296,7 @@
         <v>38</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>234.669</v>
+        <v>287.67</v>
       </c>
     </row>
     <row r="92">
@@ -16381,7 +16381,7 @@
         <v>38</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>-396.719</v>
+        <v>-396.654</v>
       </c>
     </row>
     <row r="97">
@@ -16466,7 +16466,7 @@
         <v>38</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>116.655</v>
+        <v>234.17</v>
       </c>
     </row>
     <row r="102">
@@ -16551,7 +16551,7 @@
         <v>38</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>372.594</v>
+        <v>757.01</v>
       </c>
     </row>
     <row r="107">
@@ -16636,15 +16636,15 @@
         <v>38</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>63.348</v>
+        <v>128.64</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B112" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C112" t="s">
         <v>31</v>
@@ -16653,15 +16653,15 @@
         <v>32</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>662.259</v>
+        <v>-69.164</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B113" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C113" t="s">
         <v>33</v>
@@ -16670,15 +16670,15 @@
         <v>34</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>-68.712</v>
+        <v>-64.03</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B114" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C114" t="s">
         <v>33</v>
@@ -16687,15 +16687,15 @@
         <v>35</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>-188.952</v>
+        <v>408.479</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B115" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C115" t="s">
         <v>37</v>
@@ -16704,15 +16704,15 @@
         <v>34</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>188.614</v>
+        <v>412.489</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B116" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C116" t="s">
         <v>38</v>
@@ -16721,15 +16721,15 @@
         <v>38</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>16.207</v>
+        <v>-61.253</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="B117" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="C117" t="s">
         <v>31</v>
@@ -16738,15 +16738,15 @@
         <v>32</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>-69.164</v>
+        <v>662.259</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="B118" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="C118" t="s">
         <v>33</v>
@@ -16755,15 +16755,15 @@
         <v>34</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>-64.03</v>
+        <v>-68.712</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="B119" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="C119" t="s">
         <v>33</v>
@@ -16772,15 +16772,15 @@
         <v>35</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>408.479</v>
+        <v>-188.952</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="B120" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="C120" t="s">
         <v>37</v>
@@ -16789,15 +16789,15 @@
         <v>34</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>412.489</v>
+        <v>188.614</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="B121" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="C121" t="s">
         <v>38</v>
@@ -16806,7 +16806,7 @@
         <v>38</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>-0.986</v>
+        <v>43.688</v>
       </c>
     </row>
     <row r="122">
@@ -16976,7 +16976,7 @@
         <v>38</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>-116.185</v>
+        <v>-135.218</v>
       </c>
     </row>
     <row r="132">
@@ -17061,7 +17061,7 @@
         <v>38</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>-214.897</v>
+        <v>-424.284</v>
       </c>
     </row>
     <row r="137">
@@ -17146,7 +17146,7 @@
         <v>38</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>-45.174</v>
+        <v>-37.004</v>
       </c>
     </row>
     <row r="142">
@@ -17231,7 +17231,7 @@
         <v>38</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>-159.313</v>
+        <v>-255.994</v>
       </c>
     </row>
     <row r="147">
@@ -17316,7 +17316,7 @@
         <v>38</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>-5.59</v>
+        <v>-10.988</v>
       </c>
     </row>
   </sheetData>
@@ -17368,7 +17368,7 @@
         <v>32</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-193635.592</v>
+        <v>-196576.139</v>
       </c>
     </row>
     <row r="3">
@@ -17470,7 +17470,7 @@
         <v>32</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>4309.501</v>
+        <v>4357.181</v>
       </c>
     </row>
     <row r="9">
@@ -17572,7 +17572,7 @@
         <v>32</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-3957.8</v>
+        <v>-4001.669</v>
       </c>
     </row>
     <row r="15">
@@ -17674,7 +17674,7 @@
         <v>32</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-22336.894</v>
+        <v>-22528.495</v>
       </c>
     </row>
     <row r="21">
@@ -17776,7 +17776,7 @@
         <v>32</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>94438.913</v>
+        <v>94465.457</v>
       </c>
     </row>
     <row r="27">
@@ -17878,7 +17878,7 @@
         <v>32</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>8238.173</v>
+        <v>8297.146</v>
       </c>
     </row>
     <row r="33">
@@ -18082,7 +18082,7 @@
         <v>32</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>-11913.926</v>
+        <v>-12284.431</v>
       </c>
     </row>
     <row r="45">
@@ -18184,7 +18184,7 @@
         <v>32</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>2013.019</v>
+        <v>2214.79</v>
       </c>
     </row>
     <row r="51">
@@ -18286,7 +18286,7 @@
         <v>32</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>35911.52</v>
+        <v>35939.675</v>
       </c>
     </row>
     <row r="57">
@@ -18490,7 +18490,7 @@
         <v>32</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>-235.97</v>
+        <v>-235.499</v>
       </c>
     </row>
     <row r="69">
@@ -18592,7 +18592,7 @@
         <v>32</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>-2236.48</v>
+        <v>-2224.033</v>
       </c>
     </row>
     <row r="75">
@@ -18694,7 +18694,7 @@
         <v>32</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>-2912.737</v>
+        <v>-2912.89</v>
       </c>
     </row>
     <row r="81">
@@ -18898,7 +18898,7 @@
         <v>32</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>-696.734</v>
+        <v>-833.329</v>
       </c>
     </row>
     <row r="93">
@@ -19204,7 +19204,7 @@
         <v>32</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>2891.489</v>
+        <v>3217.324</v>
       </c>
     </row>
     <row r="111">
@@ -19408,7 +19408,7 @@
         <v>32</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>1899.528</v>
+        <v>1904.215</v>
       </c>
     </row>
     <row r="123">
@@ -19510,7 +19510,7 @@
         <v>32</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>-317.634</v>
+        <v>-281.303</v>
       </c>
     </row>
     <row r="129">
@@ -19612,7 +19612,7 @@
         <v>32</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>32436.563</v>
+        <v>32406.978</v>
       </c>
     </row>
     <row r="135">
@@ -19714,7 +19714,7 @@
         <v>32</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>-345.639</v>
+        <v>-345.881</v>
       </c>
     </row>
     <row r="141">
@@ -19918,7 +19918,7 @@
         <v>32</v>
       </c>
       <c r="E152" s="2" t="n">
-        <v>6118.799</v>
+        <v>6118.683</v>
       </c>
     </row>
     <row r="153">
@@ -20020,7 +20020,7 @@
         <v>32</v>
       </c>
       <c r="E158" s="2" t="n">
-        <v>-1324.715</v>
+        <v>-1275.442</v>
       </c>
     </row>
     <row r="159">
@@ -20224,7 +20224,7 @@
         <v>32</v>
       </c>
       <c r="E170" s="2" t="n">
-        <v>10127.502</v>
+        <v>10124.912</v>
       </c>
     </row>
     <row r="171">
@@ -20326,7 +20326,7 @@
         <v>32</v>
       </c>
       <c r="E176" s="2" t="n">
-        <v>-235.388</v>
+        <v>-236.46</v>
       </c>
     </row>
     <row r="177">
@@ -20565,7 +20565,7 @@
         <v>38</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>205.096</v>
+        <v>410.193</v>
       </c>
     </row>
     <row r="9">
@@ -20684,7 +20684,7 @@
         <v>38</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-19.049</v>
+        <v>-38.099</v>
       </c>
     </row>
     <row r="16">
@@ -20803,7 +20803,7 @@
         <v>38</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>50.757</v>
+        <v>101.515</v>
       </c>
     </row>
     <row r="23">
@@ -20922,7 +20922,7 @@
         <v>38</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>99.97</v>
+        <v>199.94</v>
       </c>
     </row>
     <row r="30">
@@ -21041,7 +21041,7 @@
         <v>38</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>17.858</v>
+        <v>35.716</v>
       </c>
     </row>
     <row r="37">
@@ -21160,7 +21160,7 @@
         <v>38</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>47.002</v>
+        <v>94.004</v>
       </c>
     </row>
     <row r="44">
@@ -21279,7 +21279,7 @@
         <v>38</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>5.213</v>
+        <v>10.425</v>
       </c>
     </row>
     <row r="51">
@@ -21398,7 +21398,7 @@
         <v>38</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>-30.016</v>
+        <v>-60.033</v>
       </c>
     </row>
     <row r="58">
@@ -21517,7 +21517,7 @@
         <v>38</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>-9.024</v>
+        <v>-18.049</v>
       </c>
     </row>
     <row r="65">
@@ -21636,7 +21636,7 @@
         <v>38</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>-10.362</v>
+        <v>-20.725</v>
       </c>
     </row>
     <row r="72">
@@ -21755,7 +21755,7 @@
         <v>38</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>1.343</v>
+        <v>2.685</v>
       </c>
     </row>
     <row r="79">
@@ -21874,7 +21874,7 @@
         <v>38</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>1.365</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="86">
@@ -21993,7 +21993,7 @@
         <v>38</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>-53.15</v>
+        <v>-106.3</v>
       </c>
     </row>
     <row r="93">
@@ -22112,7 +22112,7 @@
         <v>38</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>-7.535</v>
+        <v>-15.069</v>
       </c>
     </row>
     <row r="100">
@@ -22231,7 +22231,7 @@
         <v>38</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>-1.216</v>
+        <v>-2.432</v>
       </c>
     </row>
     <row r="107">
@@ -22350,7 +22350,7 @@
         <v>38</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>3.045</v>
+        <v>6.089</v>
       </c>
     </row>
     <row r="114">
@@ -22469,7 +22469,7 @@
         <v>38</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>-15.954</v>
+        <v>-31.907</v>
       </c>
     </row>
     <row r="121">
@@ -22588,7 +22588,7 @@
         <v>38</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>23.422</v>
+        <v>46.844</v>
       </c>
     </row>
     <row r="128">
@@ -22707,7 +22707,7 @@
         <v>38</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>-4.486</v>
+        <v>-8.972</v>
       </c>
     </row>
     <row r="135">
@@ -22826,7 +22826,7 @@
         <v>38</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>-49.151</v>
+        <v>-98.302</v>
       </c>
     </row>
     <row r="142">
@@ -22945,7 +22945,7 @@
         <v>38</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>-7.835</v>
+        <v>-15.67</v>
       </c>
     </row>
     <row r="149">
@@ -23064,7 +23064,7 @@
         <v>38</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>-17.82</v>
+        <v>-35.64</v>
       </c>
     </row>
     <row r="156">
@@ -23183,7 +23183,7 @@
         <v>38</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>-25.617</v>
+        <v>-51.233</v>
       </c>
     </row>
     <row r="163">
@@ -23302,7 +23302,7 @@
         <v>38</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>9.308</v>
+        <v>18.616</v>
       </c>
     </row>
     <row r="170">
@@ -23421,7 +23421,7 @@
         <v>38</v>
       </c>
       <c r="E176" s="2" t="n">
-        <v>4.002</v>
+        <v>8.004</v>
       </c>
     </row>
     <row r="177">
@@ -23540,7 +23540,7 @@
         <v>38</v>
       </c>
       <c r="E183" s="2" t="n">
-        <v>-3.948</v>
+        <v>-7.896</v>
       </c>
     </row>
     <row r="184">
@@ -23659,7 +23659,7 @@
         <v>38</v>
       </c>
       <c r="E190" s="2" t="n">
-        <v>-40.018</v>
+        <v>-80.036</v>
       </c>
     </row>
     <row r="191">
@@ -23778,7 +23778,7 @@
         <v>38</v>
       </c>
       <c r="E197" s="2" t="n">
-        <v>-3.65</v>
+        <v>-7.3</v>
       </c>
     </row>
     <row r="198">
@@ -23897,7 +23897,7 @@
         <v>38</v>
       </c>
       <c r="E204" s="2" t="n">
-        <v>-40.297</v>
+        <v>-80.594</v>
       </c>
     </row>
     <row r="205">
@@ -24016,7 +24016,7 @@
         <v>38</v>
       </c>
       <c r="E211" s="2" t="n">
-        <v>-14.968</v>
+        <v>-29.936</v>
       </c>
     </row>
   </sheetData>
@@ -31346,7 +31346,7 @@
         <v>38</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1896.555</v>
+        <v>3387.634</v>
       </c>
     </row>
     <row r="7">
@@ -31431,7 +31431,7 @@
         <v>38</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-66.076</v>
+        <v>-136.186</v>
       </c>
     </row>
     <row r="12">
@@ -31516,7 +31516,7 @@
         <v>38</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-228.992</v>
+        <v>-428.154</v>
       </c>
     </row>
     <row r="17">
@@ -31601,7 +31601,7 @@
         <v>38</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-238.553</v>
+        <v>-433.034</v>
       </c>
     </row>
     <row r="22">
@@ -31686,7 +31686,7 @@
         <v>38</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-1.455</v>
+        <v>-2.46</v>
       </c>
     </row>
     <row r="27">
@@ -31771,7 +31771,7 @@
         <v>38</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>-129.801</v>
+        <v>-265.675</v>
       </c>
     </row>
     <row r="32">
@@ -31856,7 +31856,7 @@
         <v>38</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>-35.543</v>
+        <v>-51.753</v>
       </c>
     </row>
     <row r="37">
@@ -31941,7 +31941,7 @@
         <v>38</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>-0.988</v>
+        <v>-1.486</v>
       </c>
     </row>
     <row r="42">
@@ -32026,7 +32026,7 @@
         <v>38</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>-11.895</v>
+        <v>-16.005</v>
       </c>
     </row>
     <row r="47">
@@ -32111,7 +32111,7 @@
         <v>38</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>-44.417</v>
+        <v>-74.139</v>
       </c>
     </row>
     <row r="52">
@@ -32196,7 +32196,7 @@
         <v>38</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>-8.202</v>
+        <v>-9.414</v>
       </c>
     </row>
     <row r="57">
@@ -32281,7 +32281,7 @@
         <v>38</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>-21.522</v>
+        <v>-32.24</v>
       </c>
     </row>
     <row r="62">
@@ -32366,7 +32366,7 @@
         <v>38</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>-24.257</v>
+        <v>-39.604</v>
       </c>
     </row>
     <row r="67">
@@ -32451,7 +32451,7 @@
         <v>38</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>-123.681</v>
+        <v>-213.466</v>
       </c>
     </row>
     <row r="72">
@@ -32536,7 +32536,7 @@
         <v>38</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>-154.911</v>
+        <v>-275</v>
       </c>
     </row>
     <row r="77">
@@ -32621,7 +32621,7 @@
         <v>38</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>-25.88</v>
+        <v>-48.023</v>
       </c>
     </row>
     <row r="82">
@@ -32706,7 +32706,7 @@
         <v>38</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>-21.336</v>
+        <v>-45.608</v>
       </c>
     </row>
     <row r="87">
@@ -32791,7 +32791,7 @@
         <v>38</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>-67.389</v>
+        <v>-126.127</v>
       </c>
     </row>
     <row r="92">
@@ -32876,7 +32876,7 @@
         <v>38</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>-2.219</v>
+        <v>-4.664</v>
       </c>
     </row>
     <row r="97">
@@ -32961,7 +32961,7 @@
         <v>38</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>-24.715</v>
+        <v>-45.571</v>
       </c>
     </row>
     <row r="102">
@@ -33046,15 +33046,15 @@
         <v>38</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>-12.486</v>
+        <v>-22.79</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B107" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C107" t="s">
         <v>31</v>
@@ -33063,15 +33063,15 @@
         <v>32</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>161.219</v>
+        <v>1005.212</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B108" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C108" t="s">
         <v>33</v>
@@ -33080,15 +33080,15 @@
         <v>35</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>4993.224</v>
+        <v>-96.166</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B109" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C109" t="s">
         <v>37</v>
@@ -33097,15 +33097,15 @@
         <v>34</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>-451.456</v>
+        <v>-189.182</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C110" t="s">
         <v>37</v>
@@ -33114,15 +33114,15 @@
         <v>36</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>-1.45</v>
+        <v>-23.058</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B111" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C111" t="s">
         <v>38</v>
@@ -33131,15 +33131,15 @@
         <v>38</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>-6.153</v>
+        <v>-37.021</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B112" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C112" t="s">
         <v>31</v>
@@ -33148,15 +33148,15 @@
         <v>32</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>1005.212</v>
+        <v>161.219</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B113" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C113" t="s">
         <v>33</v>
@@ -33165,15 +33165,15 @@
         <v>35</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>-96.166</v>
+        <v>4993.224</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B114" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C114" t="s">
         <v>37</v>
@@ -33182,15 +33182,15 @@
         <v>34</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>-189.182</v>
+        <v>-451.456</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B115" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C115" t="s">
         <v>37</v>
@@ -33199,15 +33199,15 @@
         <v>36</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>-23.058</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B116" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C116" t="s">
         <v>38</v>
@@ -33216,7 +33216,7 @@
         <v>38</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>-30.039</v>
+        <v>-10.857</v>
       </c>
     </row>
     <row r="117">
@@ -33301,7 +33301,7 @@
         <v>38</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>-14.329</v>
+        <v>-43.862</v>
       </c>
     </row>
     <row r="122">
@@ -33386,7 +33386,7 @@
         <v>38</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>-16.548</v>
+        <v>-27.142</v>
       </c>
     </row>
     <row r="127">
@@ -33471,15 +33471,15 @@
         <v>38</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>-81.084</v>
+        <v>-147.406</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B132" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C132" t="s">
         <v>31</v>
@@ -33488,15 +33488,15 @@
         <v>32</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>-25.627</v>
+        <v>-63.979</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B133" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C133" t="s">
         <v>33</v>
@@ -33505,15 +33505,15 @@
         <v>35</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>-70.305</v>
+        <v>-327.467</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B134" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C134" t="s">
         <v>37</v>
@@ -33522,15 +33522,15 @@
         <v>34</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>-316.218</v>
+        <v>-889.505</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B135" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C135" t="s">
         <v>37</v>
@@ -33539,15 +33539,15 @@
         <v>36</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>-12.194</v>
+        <v>-35.065</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B136" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C136" t="s">
         <v>38</v>
@@ -33556,15 +33556,15 @@
         <v>38</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>-18.502</v>
+        <v>-155.019</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="B137" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C137" t="s">
         <v>31</v>
@@ -33573,15 +33573,15 @@
         <v>32</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>-63.979</v>
+        <v>-25.627</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="B138" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C138" t="s">
         <v>33</v>
@@ -33590,15 +33590,15 @@
         <v>35</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>-327.467</v>
+        <v>-70.305</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="B139" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C139" t="s">
         <v>37</v>
@@ -33607,15 +33607,15 @@
         <v>34</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>-889.505</v>
+        <v>-316.218</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="B140" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C140" t="s">
         <v>37</v>
@@ -33624,15 +33624,15 @@
         <v>36</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>-35.065</v>
+        <v>-12.194</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="B141" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C141" t="s">
         <v>38</v>
@@ -33641,7 +33641,7 @@
         <v>38</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>-95.042</v>
+        <v>-24.809</v>
       </c>
     </row>
     <row r="142">
@@ -33726,7 +33726,7 @@
         <v>38</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>-14.148</v>
+        <v>-23.93</v>
       </c>
     </row>
     <row r="147">
@@ -33811,7 +33811,7 @@
         <v>38</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>-3.898</v>
+        <v>-8.574</v>
       </c>
     </row>
   </sheetData>
@@ -33965,7 +33965,7 @@
         <v>38</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-157.425</v>
+        <v>-156.317</v>
       </c>
     </row>
     <row r="9">
@@ -34084,7 +34084,7 @@
         <v>38</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.076</v>
+        <v>-0.151</v>
       </c>
     </row>
     <row r="16">
@@ -34441,7 +34441,7 @@
         <v>38</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>24.635</v>
+        <v>24.014</v>
       </c>
     </row>
     <row r="37">
@@ -34764,7 +34764,7 @@
         <v>38</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>10.636</v>
+        <v>10.855</v>
       </c>
     </row>
     <row r="56">
@@ -35104,7 +35104,7 @@
         <v>38</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>-0.058</v>
+        <v>-0.116</v>
       </c>
     </row>
     <row r="76">
@@ -35342,7 +35342,7 @@
         <v>38</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>242.619</v>
+        <v>324.261</v>
       </c>
     </row>
     <row r="90">
@@ -35801,7 +35801,7 @@
         <v>38</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>3.662</v>
+        <v>3.519</v>
       </c>
     </row>
     <row r="117">
@@ -36039,7 +36039,7 @@
         <v>38</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>-76.321</v>
+        <v>-76.102</v>
       </c>
     </row>
     <row r="131">
@@ -36974,7 +36974,7 @@
         <v>38</v>
       </c>
       <c r="E185" s="2" t="n">
-        <v>-0.053</v>
+        <v>-0.175</v>
       </c>
     </row>
     <row r="186">
@@ -37093,7 +37093,7 @@
         <v>38</v>
       </c>
       <c r="E192" s="2" t="n">
-        <v>-73.181</v>
+        <v>-141.514</v>
       </c>
     </row>
     <row r="193">
